--- a/Files/ETF.xlsx
+++ b/Files/ETF.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro/Downloads/andcappe_zip/Dashboard/SITO_WEB/Sito personale/portafoglio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63A187E-FC00-B944-93E2-0AC5FF0FAB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC11CF7-0E93-5940-A76B-7711893FA9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4380" yWindow="0" windowWidth="24420" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
-    <sheet name="Foglio21" sheetId="29" r:id="rId2"/>
-    <sheet name="Foglio22" sheetId="30" r:id="rId3"/>
+    <sheet name="Foglio21" sheetId="29" r:id="rId1"/>
+    <sheet name="Foglio22" sheetId="30" r:id="rId2"/>
+    <sheet name="Foglio1" sheetId="2" r:id="rId3"/>
     <sheet name="Foglio20" sheetId="28" r:id="rId4"/>
     <sheet name="Foglio19" sheetId="27" r:id="rId5"/>
     <sheet name="Foglio18" sheetId="26" r:id="rId6"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7552" uniqueCount="2728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7586" uniqueCount="2756">
   <si>
     <t>Simbolo</t>
   </si>
@@ -8476,25 +8476,109 @@
     <t>CSBGE3.MI</t>
   </si>
   <si>
-    <t>iShares VII PLC - iShares € Govt Bond 1-3yr</t>
-  </si>
-  <si>
-    <t>iShares VII PLC - iShares € Govt Bond 3-7yr</t>
-  </si>
-  <si>
     <t>SXRQ.DE</t>
   </si>
   <si>
-    <t>iShares VII PLC - iShares € Govt Bond 7-10yr</t>
-  </si>
-  <si>
     <t>XEIN.DE</t>
   </si>
   <si>
-    <t>Xtrackers II Global Inflation-Linked Bond UCITS ETF 1C - EUR Hedged</t>
-  </si>
-  <si>
-    <t>State Street SPDR FTSE Global Convertible Bond hdg</t>
+    <t>Alternative</t>
+  </si>
+  <si>
+    <t>Az. ACWI</t>
+  </si>
+  <si>
+    <t>Az.USA Nasdaq100</t>
+  </si>
+  <si>
+    <t>Az. USA SP500</t>
+  </si>
+  <si>
+    <t>Az. USA Growth SP500</t>
+  </si>
+  <si>
+    <t>Az. USA Growth</t>
+  </si>
+  <si>
+    <t>Az.  USA Value SP500</t>
+  </si>
+  <si>
+    <t>Az USA Value Small Cap</t>
+  </si>
+  <si>
+    <t>Az. World Value Factor</t>
+  </si>
+  <si>
+    <t>Az EUROPA Value Small Cap</t>
+  </si>
+  <si>
+    <t>Az USA Small Cap Russell2000</t>
+  </si>
+  <si>
+    <t>Az. World</t>
+  </si>
+  <si>
+    <t>Az. Europe Stoxx 600</t>
+  </si>
+  <si>
+    <t>Az. Emerging Market</t>
+  </si>
+  <si>
+    <t>OB. Govt Bond 1-3yr</t>
+  </si>
+  <si>
+    <t>Ob. Govt Bond 3-7yr</t>
+  </si>
+  <si>
+    <t>Ob. Govt Bond 7-10yr</t>
+  </si>
+  <si>
+    <t>Ob. Corp Bond 1-3yr UCITS ETF</t>
+  </si>
+  <si>
+    <t>Ob. EUR Corporate Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ob. EUR High Yield Corporate Bond </t>
+  </si>
+  <si>
+    <t>Ob. Eurozone Infl-Linked Bond</t>
+  </si>
+  <si>
+    <t>Ob. Global Inflation-Linked Hedged</t>
+  </si>
+  <si>
+    <t>Ob. Global Convertible Bond hdg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold </t>
+  </si>
+  <si>
+    <t>Azionario ACWI Vanguard</t>
+  </si>
+  <si>
+    <t>AZ. USA Info Tech SP500</t>
+  </si>
+  <si>
+    <t>Azionari Tech Sp500</t>
+  </si>
+  <si>
+    <t>JEGA.MI</t>
+  </si>
+  <si>
+    <t>Alt. MF</t>
+  </si>
+  <si>
+    <t>Alt. Inf.Br.</t>
+  </si>
+  <si>
+    <t>Alt. Eu.Def</t>
+  </si>
+  <si>
+    <t>Alt. Pr.Inc.Ac</t>
+  </si>
+  <si>
+    <t>Bench AZ. VANGUARD ACWI</t>
   </si>
 </sst>
 </file>
@@ -8513,7 +8597,7 @@
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="99">
+  <fonts count="106">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -9135,21 +9219,68 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial Nova"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF232A31"/>
-      <name val="Arial Nova"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
-      <name val="Arial Nova"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF232A31"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Abadi"/>
     </font>
   </fonts>
   <fills count="12">
@@ -9423,7 +9554,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -9729,15 +9860,35 @@
     <xf numFmtId="0" fontId="87" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="96" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="96" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="99" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="96" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="99" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="98" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="101" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="101" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -9748,6 +9899,22 @@
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="102" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="102" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="104" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="104" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -9755,7 +9922,7 @@
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Percentuale" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -9767,9 +9934,77 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
+        <name val="Abadi"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Abadi"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Abadi"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Abadi"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Abadi"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -9786,8 +10021,9 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
@@ -9803,8 +10039,9 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
@@ -9820,8 +10057,9 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
@@ -9837,8 +10075,9 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
@@ -9854,75 +10093,31 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial Nova"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <name val="Arial Nova"/>
+        <sz val="9"/>
+        <name val="Abadi"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -16109,26 +16304,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{246183AC-3204-9D4E-95E8-61DE399D8F79}" name="Tabella32" displayName="Tabella32" ref="A1:D26" totalsRowShown="0" dataDxfId="9">
-  <autoFilter ref="A1:D26" xr:uid="{246183AC-3204-9D4E-95E8-61DE399D8F79}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{246183AC-3204-9D4E-95E8-61DE399D8F79}" name="Tabella32" displayName="Tabella32" ref="A1:D30" totalsRowShown="0" headerRowDxfId="11" dataDxfId="0">
+  <autoFilter ref="A1:D30" xr:uid="{246183AC-3204-9D4E-95E8-61DE399D8F79}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12AF85F4-CF3E-1A44-9197-52CD700ECF69}" name="SIMBOLO" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D2DEAFE7-7181-F841-96D9-E16F6CD58118}" name="DESCRIZIONE" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{036B7D95-54D0-CE4A-A97C-6EC741E876E4}" name="VALUTA" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{BC856CD8-BE7C-D246-AFFE-8A0458341DA0}" name="CLASSE" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{12AF85F4-CF3E-1A44-9197-52CD700ECF69}" name="SIMBOLO" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D2DEAFE7-7181-F841-96D9-E16F6CD58118}" name="DESCRIZIONE" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{036B7D95-54D0-CE4A-A97C-6EC741E876E4}" name="VALUTA" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{BC856CD8-BE7C-D246-AFFE-8A0458341DA0}" name="CLASSE" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{48919E7F-61A8-DB47-85A6-D1B66A3AD480}" name="Tabella323" displayName="Tabella323" ref="A1:D53" totalsRowShown="0" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{48919E7F-61A8-DB47-85A6-D1B66A3AD480}" name="Tabella323" displayName="Tabella323" ref="A1:D53" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:D53" xr:uid="{48919E7F-61A8-DB47-85A6-D1B66A3AD480}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{99BE53A6-82BE-7C4C-8EDB-FC2585DE7E29}" name="SIMBOLO" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{79CB9D70-57D7-004E-8DD2-11CA0A269F24}" name="DESCRIZIONE" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{4221CAB4-B4C0-5746-BDF4-C3FC111D5F78}" name="VALUTA" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{530400BE-E6AA-4A47-B046-BF29D0205198}" name="CLASSE" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{99BE53A6-82BE-7C4C-8EDB-FC2585DE7E29}" name="SIMBOLO" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{79CB9D70-57D7-004E-8DD2-11CA0A269F24}" name="DESCRIZIONE" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{4221CAB4-B4C0-5746-BDF4-C3FC111D5F78}" name="VALUTA" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{530400BE-E6AA-4A47-B046-BF29D0205198}" name="CLASSE" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17238,2066 +17433,451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A71EAAD3-1C46-AE43-AEF2-56898A879CDD}">
-  <dimension ref="A1:J178"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C714FF38-E71E-3648-9A7A-13401C8B9393}">
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="11"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="48.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" style="233" customWidth="1"/>
+    <col min="2" max="2" width="106.5" style="233" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="233"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23">
-      <c r="A1" s="18" t="s">
-        <v>710</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="197" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="198" t="s">
-        <v>2549</v>
-      </c>
-      <c r="C2" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="197" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B3" s="198" t="s">
-        <v>2550</v>
-      </c>
-      <c r="C3" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:10" ht="45">
-      <c r="A4" s="180" t="s">
-        <v>2574</v>
-      </c>
-      <c r="B4" s="198" t="s">
-        <v>2605</v>
-      </c>
-      <c r="C4" s="199" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="197" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B5" s="198" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C5" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="12"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="197" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="231" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1" s="232" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C1" s="233" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D1" s="233" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="12">
+      <c r="A2" s="238" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="239" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C2" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="240" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12">
+      <c r="A3" s="241" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B3" s="241" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C3" s="242" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="243" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12">
+      <c r="A4" s="240" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B4" s="241" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C4" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="243" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="12">
+      <c r="A5" s="241" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B5" s="241" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C5" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="243" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="12">
+      <c r="A6" s="240" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B6" s="241" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C6" s="244" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="243" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="12">
+      <c r="A7" s="238" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B7" s="241" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C7" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="240" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="12">
+      <c r="A8" s="240" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B8" s="241" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C8" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="240" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="12">
+      <c r="A9" s="240" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B9" s="241" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C9" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="240" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="12">
+      <c r="A10" s="240" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="240" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C10" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="240" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="12">
+      <c r="A11" s="240" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B11" s="240" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C11" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="240" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="12">
+      <c r="A12" s="240" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B12" s="240" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C12" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="240" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="12">
+      <c r="A13" s="245" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B13" s="240" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C13" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="240" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="12">
+      <c r="A14" s="240" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B14" s="240" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C14" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="240" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="12">
+      <c r="A15" s="240" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B15" s="240" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C15" s="240" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="240" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12">
+      <c r="A16" s="245" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="198" t="s">
-        <v>2552</v>
-      </c>
-      <c r="C6" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="197" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="198" t="s">
-        <v>2553</v>
-      </c>
-      <c r="C7" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="12"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="197" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B8" s="198" t="s">
-        <v>2554</v>
-      </c>
-      <c r="C8" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="197" t="s">
-        <v>2255</v>
-      </c>
-      <c r="B9" s="198" t="s">
-        <v>2555</v>
-      </c>
-      <c r="C9" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="197" t="s">
-        <v>1757</v>
-      </c>
-      <c r="B10" s="198" t="s">
-        <v>2556</v>
-      </c>
-      <c r="C10" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="197" t="s">
-        <v>2259</v>
-      </c>
-      <c r="B11" s="198" t="s">
-        <v>2557</v>
-      </c>
-      <c r="C11" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10" ht="23">
-      <c r="A12" s="197" t="s">
-        <v>2196</v>
-      </c>
-      <c r="B12" s="198" t="s">
-        <v>2558</v>
-      </c>
-      <c r="C12" s="199" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="197" t="s">
-        <v>2188</v>
-      </c>
-      <c r="B13" s="198" t="s">
-        <v>2559</v>
-      </c>
-      <c r="C13" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="197" t="s">
-        <v>2231</v>
-      </c>
-      <c r="B14" s="198" t="s">
-        <v>2560</v>
-      </c>
-      <c r="C14" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="197" t="s">
-        <v>2242</v>
-      </c>
-      <c r="B15" s="198" t="s">
-        <v>2561</v>
-      </c>
-      <c r="C15" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="197" t="s">
-        <v>2244</v>
-      </c>
-      <c r="B16" s="198" t="s">
-        <v>2562</v>
-      </c>
-      <c r="C16" s="199" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="197" t="s">
-        <v>2240</v>
-      </c>
-      <c r="B17" s="198" t="s">
-        <v>2375</v>
-      </c>
-      <c r="C17" s="199" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="15"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="197" t="s">
-        <v>2320</v>
-      </c>
-      <c r="B18" s="198" t="s">
-        <v>2321</v>
-      </c>
-      <c r="C18" s="199" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="197" t="s">
-        <v>2343</v>
-      </c>
-      <c r="B19" s="198" t="s">
-        <v>2532</v>
-      </c>
-      <c r="C19" s="199" t="s">
-        <v>2345</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" ht="45">
-      <c r="A20" s="180" t="s">
-        <v>2571</v>
-      </c>
-      <c r="B20" s="180" t="s">
-        <v>2572</v>
-      </c>
-      <c r="C20" s="219" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" ht="45">
-      <c r="A21" s="19" t="s">
-        <v>2255</v>
-      </c>
-      <c r="B21" s="180" t="s">
-        <v>2614</v>
-      </c>
-      <c r="C21" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" ht="45">
-      <c r="A22" s="19" t="s">
-        <v>2615</v>
-      </c>
-      <c r="B22" s="180" t="s">
-        <v>2616</v>
-      </c>
-      <c r="C22" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="I22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" ht="45">
-      <c r="A23" s="19" t="s">
-        <v>2617</v>
-      </c>
-      <c r="B23" s="180" t="s">
-        <v>2618</v>
-      </c>
-      <c r="C23" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" ht="45">
-      <c r="A24" s="180" t="s">
-        <v>2576</v>
-      </c>
-      <c r="B24" s="180" t="s">
-        <v>2577</v>
-      </c>
-      <c r="C24" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" ht="45">
-      <c r="A25" s="180" t="s">
-        <v>2202</v>
-      </c>
-      <c r="B25" s="180" t="s">
-        <v>2575</v>
-      </c>
-      <c r="C25" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" ht="45">
-      <c r="A26" s="180" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B26" s="180" t="s">
-        <v>2606</v>
-      </c>
-      <c r="C26" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" ht="45">
-      <c r="A27" s="180" t="s">
-        <v>2607</v>
-      </c>
-      <c r="B27" s="180" t="s">
-        <v>2608</v>
-      </c>
-      <c r="C27" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="1:9" ht="45">
-      <c r="A28" s="180" t="s">
-        <v>2609</v>
-      </c>
-      <c r="B28" s="180" t="s">
-        <v>2610</v>
-      </c>
-      <c r="C28" s="220" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" ht="45">
-      <c r="A29" s="180" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B29" s="180" t="s">
-        <v>2611</v>
-      </c>
-      <c r="C29" s="220" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" ht="45">
-      <c r="A30" s="180" t="s">
-        <v>2612</v>
-      </c>
-      <c r="B30" s="180" t="s">
-        <v>2613</v>
-      </c>
-      <c r="C30" s="220" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="1:9" ht="18">
-      <c r="A31" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="18">
-      <c r="A32" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18">
-      <c r="A33" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="18">
-      <c r="A34" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="18">
-      <c r="A35" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="18">
-      <c r="A36" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="18">
-      <c r="A37" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="18">
-      <c r="A38" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="18">
-      <c r="A39" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="18">
-      <c r="A40" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="18">
-      <c r="A41" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="18">
-      <c r="A42" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="18">
-      <c r="A43" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="18">
-      <c r="A44" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="18">
-      <c r="A45" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="18">
-      <c r="A46" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C46" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="18">
-      <c r="A47" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="18">
-      <c r="A48" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="18">
-      <c r="A49" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="18">
-      <c r="A50" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="B50" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C50" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="18">
-      <c r="A51" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="18">
-      <c r="A52" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="18">
-      <c r="A53" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C53" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="18">
-      <c r="A54" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C54" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="18">
-      <c r="A55" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="18">
-      <c r="A56" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="C56" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="18">
-      <c r="A57" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C57" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="18">
-      <c r="A58" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C58" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="18">
-      <c r="A59" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="18">
-      <c r="A60" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="B60" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="18">
-      <c r="A61" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="C61" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="18">
-      <c r="A62" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="C62" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="18">
-      <c r="A63" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="C63" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="18">
-      <c r="A64" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="C64" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="18">
-      <c r="A65" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="C65" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="18">
-      <c r="A66" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C66" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="18">
-      <c r="A67" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="B67" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C67" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="18">
-      <c r="A68" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C68" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="18">
-      <c r="A69" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="B69" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C69" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="18">
-      <c r="A70" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C70" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="18">
-      <c r="A71" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C71" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="18">
-      <c r="A72" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="C72" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="18">
-      <c r="A73" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C73" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="18">
-      <c r="A74" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C74" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="18">
-      <c r="A75" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C75" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="18">
-      <c r="A76" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="B76" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C76" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="18">
-      <c r="A77" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C77" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="18">
-      <c r="A78" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="B78" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="C78" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="18">
-      <c r="A79" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="B79" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="C79" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="18">
-      <c r="A80" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="B80" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="C80" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="18">
-      <c r="A81" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>288</v>
-      </c>
-      <c r="C81" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="18">
-      <c r="A82" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="B82" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="C82" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="18">
-      <c r="A83" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C83" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="18">
-      <c r="A84" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="B84" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C84" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="18">
-      <c r="A85" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="B85" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="C85" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="18">
-      <c r="A86" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="B86" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="C86" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="18">
-      <c r="A87" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="B87" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C87" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="18">
-      <c r="A88" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="B88" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C88" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="18">
-      <c r="A89" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>320</v>
-      </c>
-      <c r="C89" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="18">
-      <c r="A90" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="C90" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="18">
-      <c r="A91" s="27" t="s">
-        <v>327</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C91" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="18">
-      <c r="A92" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>332</v>
-      </c>
-      <c r="C92" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="18">
-      <c r="A93" s="27" t="s">
-        <v>335</v>
-      </c>
-      <c r="B93" s="27" t="s">
-        <v>336</v>
-      </c>
-      <c r="C93" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="18">
-      <c r="A94" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="C94" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="18">
-      <c r="A95" s="27" t="s">
-        <v>344</v>
-      </c>
-      <c r="B95" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="C95" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="18">
-      <c r="A96" s="27" t="s">
-        <v>348</v>
-      </c>
-      <c r="B96" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="C96" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="18">
-      <c r="A97" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="B97" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="C97" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="18">
-      <c r="A98" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="B98" s="27" t="s">
-        <v>357</v>
-      </c>
-      <c r="C98" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="18">
-      <c r="A99" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="B99" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="C99" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="18">
-      <c r="A100" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="B100" s="27" t="s">
-        <v>365</v>
-      </c>
-      <c r="C100" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="18">
-      <c r="A101" s="27" t="s">
-        <v>368</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C101" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="18">
-      <c r="A102" s="27" t="s">
-        <v>372</v>
-      </c>
-      <c r="B102" s="27" t="s">
-        <v>373</v>
-      </c>
-      <c r="C102" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="18">
-      <c r="A103" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="B103" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C103" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="18">
-      <c r="A104" s="27" t="s">
-        <v>380</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>381</v>
-      </c>
-      <c r="C104" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="18">
-      <c r="A105" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="B105" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="C105" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="18">
-      <c r="A106" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="B106" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="C106" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="18">
-      <c r="A107" s="27" t="s">
-        <v>392</v>
-      </c>
-      <c r="B107" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="C107" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="18">
-      <c r="A108" s="27" t="s">
-        <v>396</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>397</v>
-      </c>
-      <c r="C108" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="18">
-      <c r="A109" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="B109" s="27" t="s">
-        <v>401</v>
-      </c>
-      <c r="C109" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="18">
-      <c r="A110" s="27" t="s">
-        <v>404</v>
-      </c>
-      <c r="B110" s="27" t="s">
-        <v>405</v>
-      </c>
-      <c r="C110" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="18">
-      <c r="A111" s="27" t="s">
-        <v>408</v>
-      </c>
-      <c r="B111" s="27" t="s">
-        <v>409</v>
-      </c>
-      <c r="C111" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="18">
-      <c r="A112" s="27" t="s">
-        <v>412</v>
-      </c>
-      <c r="B112" s="27" t="s">
-        <v>413</v>
-      </c>
-      <c r="C112" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="18">
-      <c r="A113" s="27" t="s">
-        <v>416</v>
-      </c>
-      <c r="B113" s="27" t="s">
-        <v>417</v>
-      </c>
-      <c r="C113" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="18">
-      <c r="A114" s="27" t="s">
-        <v>420</v>
-      </c>
-      <c r="B114" s="27" t="s">
-        <v>421</v>
-      </c>
-      <c r="C114" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="18">
-      <c r="A115" s="27" t="s">
-        <v>424</v>
-      </c>
-      <c r="B115" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="C115" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="18">
-      <c r="A116" s="27" t="s">
-        <v>428</v>
-      </c>
-      <c r="B116" s="27" t="s">
-        <v>429</v>
-      </c>
-      <c r="C116" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="18">
-      <c r="A117" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="B117" s="27" t="s">
-        <v>433</v>
-      </c>
-      <c r="C117" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="18">
-      <c r="A118" s="27" t="s">
-        <v>436</v>
-      </c>
-      <c r="B118" s="27" t="s">
-        <v>437</v>
-      </c>
-      <c r="C118" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="18">
-      <c r="A119" s="27" t="s">
-        <v>440</v>
-      </c>
-      <c r="B119" s="27" t="s">
-        <v>441</v>
-      </c>
-      <c r="C119" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="18">
-      <c r="A120" s="27" t="s">
-        <v>444</v>
-      </c>
-      <c r="B120" s="27" t="s">
-        <v>445</v>
-      </c>
-      <c r="C120" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="18">
-      <c r="A121" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="B121" s="27" t="s">
-        <v>449</v>
-      </c>
-      <c r="C121" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="18">
-      <c r="A122" s="27" t="s">
-        <v>452</v>
-      </c>
-      <c r="B122" s="27" t="s">
-        <v>453</v>
-      </c>
-      <c r="C122" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="18">
-      <c r="A123" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="B123" s="27" t="s">
-        <v>457</v>
-      </c>
-      <c r="C123" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="18">
-      <c r="A124" s="27" t="s">
-        <v>460</v>
-      </c>
-      <c r="B124" s="27" t="s">
-        <v>461</v>
-      </c>
-      <c r="C124" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="18">
-      <c r="A125" s="27" t="s">
-        <v>464</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>465</v>
-      </c>
-      <c r="C125" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="18">
-      <c r="A126" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="B126" s="27" t="s">
-        <v>469</v>
-      </c>
-      <c r="C126" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="18">
-      <c r="A127" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="C127" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="18">
-      <c r="A128" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>477</v>
-      </c>
-      <c r="C128" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="18">
-      <c r="A129" s="27" t="s">
-        <v>480</v>
-      </c>
-      <c r="B129" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="C129" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="18">
-      <c r="A130" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="B130" s="27" t="s">
-        <v>485</v>
-      </c>
-      <c r="C130" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="18">
-      <c r="A131" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="B131" s="27" t="s">
-        <v>489</v>
-      </c>
-      <c r="C131" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="18">
-      <c r="A132" s="27" t="s">
-        <v>492</v>
-      </c>
-      <c r="B132" s="27" t="s">
-        <v>493</v>
-      </c>
-      <c r="C132" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="18">
-      <c r="A133" s="27" t="s">
-        <v>496</v>
-      </c>
-      <c r="B133" s="27" t="s">
-        <v>497</v>
-      </c>
-      <c r="C133" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="18">
-      <c r="A134" s="27" t="s">
-        <v>500</v>
-      </c>
-      <c r="B134" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="C134" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="18">
-      <c r="A135" s="27" t="s">
-        <v>504</v>
-      </c>
-      <c r="B135" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="C135" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="18">
-      <c r="A136" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="B136" s="27" t="s">
-        <v>509</v>
-      </c>
-      <c r="C136" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="18">
-      <c r="A137" s="27" t="s">
-        <v>512</v>
-      </c>
-      <c r="B137" s="27" t="s">
-        <v>513</v>
-      </c>
-      <c r="C137" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="18">
-      <c r="A138" s="27" t="s">
-        <v>516</v>
-      </c>
-      <c r="B138" s="27" t="s">
-        <v>517</v>
-      </c>
-      <c r="C138" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="18">
-      <c r="A139" s="27" t="s">
-        <v>520</v>
-      </c>
-      <c r="B139" s="27" t="s">
-        <v>521</v>
-      </c>
-      <c r="C139" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="18">
-      <c r="A140" s="27" t="s">
-        <v>524</v>
-      </c>
-      <c r="B140" s="27" t="s">
-        <v>525</v>
-      </c>
-      <c r="C140" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="18">
-      <c r="A141" s="27" t="s">
-        <v>528</v>
-      </c>
-      <c r="B141" s="27" t="s">
-        <v>529</v>
-      </c>
-      <c r="C141" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="18">
-      <c r="A142" s="27" t="s">
-        <v>532</v>
-      </c>
-      <c r="B142" s="27" t="s">
-        <v>533</v>
-      </c>
-      <c r="C142" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="18">
-      <c r="A143" s="27" t="s">
-        <v>536</v>
-      </c>
-      <c r="B143" s="27" t="s">
-        <v>537</v>
-      </c>
-      <c r="C143" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="18">
-      <c r="A144" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="B144" s="27" t="s">
-        <v>541</v>
-      </c>
-      <c r="C144" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="18">
-      <c r="A145" s="27" t="s">
-        <v>544</v>
-      </c>
-      <c r="B145" s="27" t="s">
-        <v>545</v>
-      </c>
-      <c r="C145" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="18">
-      <c r="A146" s="27" t="s">
-        <v>548</v>
-      </c>
-      <c r="B146" s="27" t="s">
-        <v>549</v>
-      </c>
-      <c r="C146" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="18">
-      <c r="A147" s="27" t="s">
-        <v>552</v>
-      </c>
-      <c r="B147" s="27" t="s">
-        <v>553</v>
-      </c>
-      <c r="C147" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="18">
-      <c r="A148" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B148" s="27" t="s">
-        <v>556</v>
-      </c>
-      <c r="C148" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="18">
-      <c r="A149" s="27" t="s">
-        <v>561</v>
-      </c>
-      <c r="B149" s="27" t="s">
-        <v>562</v>
-      </c>
-      <c r="C149" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="18">
-      <c r="A150" s="27" t="s">
-        <v>565</v>
-      </c>
-      <c r="B150" s="27" t="s">
-        <v>566</v>
-      </c>
-      <c r="C150" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="18">
-      <c r="A151" s="27" t="s">
-        <v>569</v>
-      </c>
-      <c r="B151" s="27" t="s">
-        <v>570</v>
-      </c>
-      <c r="C151" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="18">
-      <c r="A152" s="27" t="s">
-        <v>573</v>
-      </c>
-      <c r="B152" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="C152" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="18">
-      <c r="A153" s="27" t="s">
-        <v>577</v>
-      </c>
-      <c r="B153" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="C153" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="18">
-      <c r="A154" s="27" t="s">
-        <v>581</v>
-      </c>
-      <c r="B154" s="27" t="s">
-        <v>582</v>
-      </c>
-      <c r="C154" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="18">
-      <c r="A155" s="27" t="s">
-        <v>585</v>
-      </c>
-      <c r="B155" s="27" t="s">
-        <v>586</v>
-      </c>
-      <c r="C155" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="18">
-      <c r="A156" s="27" t="s">
-        <v>589</v>
-      </c>
-      <c r="B156" s="27" t="s">
-        <v>590</v>
-      </c>
-      <c r="C156" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="18">
-      <c r="A157" s="27" t="s">
-        <v>593</v>
-      </c>
-      <c r="B157" s="27" t="s">
-        <v>594</v>
-      </c>
-      <c r="C157" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="18">
-      <c r="A158" s="27" t="s">
-        <v>597</v>
-      </c>
-      <c r="B158" s="27" t="s">
-        <v>598</v>
-      </c>
-      <c r="C158" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="18">
-      <c r="A159" s="27" t="s">
-        <v>601</v>
-      </c>
-      <c r="B159" s="27" t="s">
-        <v>602</v>
-      </c>
-      <c r="C159" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="18">
-      <c r="A160" s="27" t="s">
-        <v>605</v>
-      </c>
-      <c r="B160" s="27" t="s">
-        <v>606</v>
-      </c>
-      <c r="C160" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="18">
-      <c r="A161" s="27" t="s">
-        <v>609</v>
-      </c>
-      <c r="B161" s="27" t="s">
-        <v>610</v>
-      </c>
-      <c r="C161" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="18">
-      <c r="A162" s="27" t="s">
-        <v>613</v>
-      </c>
-      <c r="B162" s="27" t="s">
-        <v>614</v>
-      </c>
-      <c r="C162" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="18">
-      <c r="A163" s="27" t="s">
-        <v>617</v>
-      </c>
-      <c r="B163" s="27" t="s">
-        <v>618</v>
-      </c>
-      <c r="C163" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="18">
-      <c r="A164" s="27" t="s">
-        <v>621</v>
-      </c>
-      <c r="B164" s="27" t="s">
-        <v>622</v>
-      </c>
-      <c r="C164" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="18">
-      <c r="A165" s="27" t="s">
-        <v>625</v>
-      </c>
-      <c r="B165" s="27" t="s">
-        <v>626</v>
-      </c>
-      <c r="C165" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="18">
-      <c r="A166" s="27" t="s">
-        <v>629</v>
-      </c>
-      <c r="B166" s="27" t="s">
-        <v>630</v>
-      </c>
-      <c r="C166" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="18">
-      <c r="A167" s="27" t="s">
-        <v>633</v>
-      </c>
-      <c r="B167" s="27" t="s">
-        <v>634</v>
-      </c>
-      <c r="C167" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="18">
-      <c r="A168" s="27" t="s">
-        <v>637</v>
-      </c>
-      <c r="B168" s="27" t="s">
-        <v>638</v>
-      </c>
-      <c r="C168" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="18">
-      <c r="A169" s="27" t="s">
-        <v>641</v>
-      </c>
-      <c r="B169" s="27" t="s">
-        <v>642</v>
-      </c>
-      <c r="C169" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="18">
-      <c r="A170" s="27" t="s">
-        <v>645</v>
-      </c>
-      <c r="B170" s="27" t="s">
-        <v>646</v>
-      </c>
-      <c r="C170" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="18">
-      <c r="A171" s="27" t="s">
-        <v>649</v>
-      </c>
-      <c r="B171" s="27" t="s">
-        <v>650</v>
-      </c>
-      <c r="C171" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="18">
-      <c r="A172" s="27" t="s">
-        <v>653</v>
-      </c>
-      <c r="B172" s="27" t="s">
-        <v>654</v>
-      </c>
-      <c r="C172" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="18">
-      <c r="A173" s="27" t="s">
-        <v>657</v>
-      </c>
-      <c r="B173" s="27" t="s">
-        <v>658</v>
-      </c>
-      <c r="C173" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="18">
-      <c r="A174" s="27" t="s">
-        <v>661</v>
-      </c>
-      <c r="B174" s="27" t="s">
-        <v>662</v>
-      </c>
-      <c r="C174" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="18">
-      <c r="A175" s="27" t="s">
-        <v>665</v>
-      </c>
-      <c r="B175" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="C175" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="18">
-      <c r="A176" s="27" t="s">
-        <v>669</v>
-      </c>
-      <c r="B176" s="27" t="s">
-        <v>670</v>
-      </c>
-      <c r="C176" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="18">
-      <c r="A177" s="27" t="s">
-        <v>673</v>
-      </c>
-      <c r="B177" s="27" t="s">
-        <v>674</v>
-      </c>
-      <c r="C177" s="172" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="18">
-      <c r="A178" s="27" t="s">
-        <v>677</v>
-      </c>
-      <c r="B178" s="27" t="s">
-        <v>678</v>
-      </c>
-      <c r="C178" s="172" t="s">
-        <v>29</v>
+      <c r="B16" s="240" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C16" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="240" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="12">
+      <c r="A17" s="240" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B17" s="240" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C17" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="240" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="12">
+      <c r="A18" s="240" t="s">
+        <v>833</v>
+      </c>
+      <c r="B18" s="240" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C18" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="240" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="12">
+      <c r="A19" s="240" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B19" s="240" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C19" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="240" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="12">
+      <c r="A20" s="240" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B20" s="240" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C20" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="240" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="12">
+      <c r="A21" s="245" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B21" s="245" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C21" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="240" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="12">
+      <c r="A22" s="245" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B22" s="245" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C22" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="240" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="12">
+      <c r="A23" s="245" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B23" s="245" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C23" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="240" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="12">
+      <c r="A24" s="240" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B24" s="240" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C24" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="240" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="12">
+      <c r="A25" s="240" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B25" s="241" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C25" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="240" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="12">
+      <c r="A26" s="240" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B26" s="241" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C26" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="240" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="12">
+      <c r="A27" s="245" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B27" s="240" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C27" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="240" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="12">
+      <c r="A28" s="245" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B28" s="245" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C28" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="240" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="12">
+      <c r="A29" s="240" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B29" s="241" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C29" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="240" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="12">
+      <c r="A30" s="240" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B30" s="240" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C30" s="240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="240" t="s">
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="95" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A27" r:id="rId1" display="http://xgin.de/" xr:uid="{6D042F4B-B1B6-714D-834A-FF03BB9AF65F}"/>
+    <hyperlink ref="A16" r:id="rId2" display="http://zprv.de/" xr:uid="{AE8F80AC-32A6-C643-BEE6-694ECBB145F6}"/>
+    <hyperlink ref="A13" r:id="rId3" display="http://iusg.de/" xr:uid="{C28C7857-119A-4744-B0BB-4DDEA3E95E35}"/>
+    <hyperlink ref="B21" r:id="rId4" display="https://finance.yahoo.com/quote/CSBGE3.MI/" xr:uid="{07F4F9CA-E0FA-1C49-87F4-4EBCF7177C7D}"/>
+    <hyperlink ref="B22" r:id="rId5" display="https://finance.yahoo.com/quote/CSBGE7.MI/" xr:uid="{02FC7EA0-25C6-E34E-AB6A-3622B551A50D}"/>
+    <hyperlink ref="B23" r:id="rId6" display="https://finance.yahoo.com/quote/SXRQ.DE/" xr:uid="{4E4D2C26-5E71-C644-AF09-EF7691622628}"/>
+    <hyperlink ref="A28" r:id="rId7" display="https://finance.yahoo.com/quote/XEIN.DE/" xr:uid="{6DA783E3-A09C-7C47-88D8-23C14B21E7FE}"/>
+    <hyperlink ref="B28" r:id="rId8" display="https://finance.yahoo.com/quote/XEIN.DE/" xr:uid="{894A731F-3358-3D4B-A900-50AD652ED5AE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId9"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -19312,20 +17892,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="236" t="s">
         <v>2346</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="229" t="s">
+      <c r="A2" s="237" t="s">
         <v>2347</v>
       </c>
-      <c r="B2" s="227"/>
-      <c r="C2" s="227"/>
-      <c r="D2" s="227"/>
+      <c r="B2" s="235"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="181" t="s">
@@ -19342,12 +17922,12 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="226" t="s">
+      <c r="A4" s="234" t="s">
         <v>2349</v>
       </c>
-      <c r="B4" s="227"/>
-      <c r="C4" s="227"/>
-      <c r="D4" s="227"/>
+      <c r="B4" s="235"/>
+      <c r="C4" s="235"/>
+      <c r="D4" s="235"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="182" t="s">
@@ -19574,12 +18154,12 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="226" t="s">
+      <c r="A21" s="234" t="s">
         <v>2377</v>
       </c>
-      <c r="B21" s="227"/>
-      <c r="C21" s="227"/>
-      <c r="D21" s="227"/>
+      <c r="B21" s="235"/>
+      <c r="C21" s="235"/>
+      <c r="D21" s="235"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="186" t="s">
@@ -19624,12 +18204,12 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="226" t="s">
+      <c r="A25" s="234" t="s">
         <v>2384</v>
       </c>
-      <c r="B25" s="227"/>
-      <c r="C25" s="227"/>
-      <c r="D25" s="227"/>
+      <c r="B25" s="235"/>
+      <c r="C25" s="235"/>
+      <c r="D25" s="235"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="186" t="s">
@@ -19674,12 +18254,12 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="226" t="s">
+      <c r="A29" s="234" t="s">
         <v>2391</v>
       </c>
-      <c r="B29" s="227"/>
-      <c r="C29" s="227"/>
-      <c r="D29" s="227"/>
+      <c r="B29" s="235"/>
+      <c r="C29" s="235"/>
+      <c r="D29" s="235"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="186" t="s">
@@ -19724,12 +18304,12 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="226" t="s">
+      <c r="A33" s="234" t="s">
         <v>2395</v>
       </c>
-      <c r="B33" s="227"/>
-      <c r="C33" s="227"/>
-      <c r="D33" s="227"/>
+      <c r="B33" s="235"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="186" t="s">
@@ -19788,12 +18368,12 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="226" t="s">
+      <c r="A38" s="234" t="s">
         <v>2403</v>
       </c>
-      <c r="B38" s="227"/>
-      <c r="C38" s="227"/>
-      <c r="D38" s="227"/>
+      <c r="B38" s="235"/>
+      <c r="C38" s="235"/>
+      <c r="D38" s="235"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="190" t="s">
@@ -19838,12 +18418,12 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="226" t="s">
+      <c r="A42" s="234" t="s">
         <v>2410</v>
       </c>
-      <c r="B42" s="227"/>
-      <c r="C42" s="227"/>
-      <c r="D42" s="227"/>
+      <c r="B42" s="235"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="190" t="s">
@@ -19888,12 +18468,12 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="226" t="s">
+      <c r="A46" s="234" t="s">
         <v>2417</v>
       </c>
-      <c r="B46" s="227"/>
-      <c r="C46" s="227"/>
-      <c r="D46" s="227"/>
+      <c r="B46" s="235"/>
+      <c r="C46" s="235"/>
+      <c r="D46" s="235"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="190" t="s">
@@ -19938,12 +18518,12 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="226" t="s">
+      <c r="A50" s="234" t="s">
         <v>2424</v>
       </c>
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
-      <c r="D50" s="227"/>
+      <c r="B50" s="235"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="190" t="s">
@@ -19988,12 +18568,12 @@
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="226" t="s">
+      <c r="A54" s="234" t="s">
         <v>2431</v>
       </c>
-      <c r="B54" s="227"/>
-      <c r="C54" s="227"/>
-      <c r="D54" s="227"/>
+      <c r="B54" s="235"/>
+      <c r="C54" s="235"/>
+      <c r="D54" s="235"/>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="190" t="s">
@@ -20038,12 +18618,12 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="226" t="s">
+      <c r="A58" s="234" t="s">
         <v>2437</v>
       </c>
-      <c r="B58" s="227"/>
-      <c r="C58" s="227"/>
-      <c r="D58" s="227"/>
+      <c r="B58" s="235"/>
+      <c r="C58" s="235"/>
+      <c r="D58" s="235"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="190" t="s">
@@ -20088,12 +18668,12 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="226" t="s">
+      <c r="A62" s="234" t="s">
         <v>2444</v>
       </c>
-      <c r="B62" s="227"/>
-      <c r="C62" s="227"/>
-      <c r="D62" s="227"/>
+      <c r="B62" s="235"/>
+      <c r="C62" s="235"/>
+      <c r="D62" s="235"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="190" t="s">
@@ -20124,12 +18704,12 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="226" t="s">
+      <c r="A65" s="234" t="s">
         <v>2449</v>
       </c>
-      <c r="B65" s="227"/>
-      <c r="C65" s="227"/>
-      <c r="D65" s="227"/>
+      <c r="B65" s="235"/>
+      <c r="C65" s="235"/>
+      <c r="D65" s="235"/>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="186" t="s">
@@ -20174,12 +18754,12 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="226" t="s">
+      <c r="A69" s="234" t="s">
         <v>2455</v>
       </c>
-      <c r="B69" s="227"/>
-      <c r="C69" s="227"/>
-      <c r="D69" s="227"/>
+      <c r="B69" s="235"/>
+      <c r="C69" s="235"/>
+      <c r="D69" s="235"/>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="186" t="s">
@@ -20210,12 +18790,12 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="226" t="s">
+      <c r="A72" s="234" t="s">
         <v>2460</v>
       </c>
-      <c r="B72" s="227"/>
-      <c r="C72" s="227"/>
-      <c r="D72" s="227"/>
+      <c r="B72" s="235"/>
+      <c r="C72" s="235"/>
+      <c r="D72" s="235"/>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="190" t="s">
@@ -20260,12 +18840,12 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="226" t="s">
+      <c r="A76" s="234" t="s">
         <v>2467</v>
       </c>
-      <c r="B76" s="227"/>
-      <c r="C76" s="227"/>
-      <c r="D76" s="227"/>
+      <c r="B76" s="235"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="235"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="190" t="s">
@@ -20310,12 +18890,12 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="226" t="s">
+      <c r="A80" s="234" t="s">
         <v>2474</v>
       </c>
-      <c r="B80" s="227"/>
-      <c r="C80" s="227"/>
-      <c r="D80" s="227"/>
+      <c r="B80" s="235"/>
+      <c r="C80" s="235"/>
+      <c r="D80" s="235"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="190" t="s">
@@ -24487,401 +23067,839 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C714FF38-E71E-3648-9A7A-13401C8B9393}">
-  <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C41D104-D122-ED4F-9557-76507CFD2D71}">
+  <dimension ref="A1:I57"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="106.5" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" style="224" customWidth="1"/>
+    <col min="2" max="2" width="78.83203125" style="224" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="224"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="224" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="225" t="s">
         <v>2120</v>
       </c>
-      <c r="B1" s="225" t="s">
+      <c r="B1" s="228" t="s">
         <v>2121</v>
       </c>
-      <c r="C1" s="221" t="s">
+      <c r="C1" s="224" t="s">
         <v>2122</v>
       </c>
-      <c r="D1" s="221" t="s">
+      <c r="D1" s="224" t="s">
         <v>2703</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="194" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="221" t="s">
+        <v>820</v>
+      </c>
+      <c r="B2" s="222" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C2" s="223" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="224" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="225" t="s">
         <v>2619</v>
       </c>
-      <c r="B2" s="222" t="s">
+      <c r="B3" s="222" t="s">
         <v>2620</v>
       </c>
-      <c r="C2" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="196" t="s">
+      <c r="C3" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="224" t="s">
         <v>2696</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="196" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="224" t="s">
         <v>2668</v>
       </c>
-      <c r="B3" s="196" t="s">
+      <c r="B4" s="224" t="s">
         <v>2669</v>
       </c>
-      <c r="C3" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="196" t="s">
+      <c r="C4" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="224" t="s">
         <v>2673</v>
       </c>
-      <c r="E3" s="48"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="196" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="226" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B5" s="224" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C5" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="224" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="224" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B6" s="224" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C6" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="224" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="224" t="s">
         <v>1089</v>
       </c>
-      <c r="B4" s="196" t="s">
+      <c r="B7" s="224" t="s">
         <v>2674</v>
       </c>
-      <c r="C4" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="196" t="s">
+      <c r="C7" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="224" t="s">
         <v>2680</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45">
-      <c r="A5" s="223" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="226" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B8" s="224" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C8" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="224" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="224" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B9" s="224" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C9" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="224" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="224" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B10" s="224" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C10" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="224" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="226" t="s">
         <v>2704</v>
       </c>
-      <c r="B5" s="180" t="s">
+      <c r="B11" s="222" t="s">
         <v>2705</v>
       </c>
-      <c r="C5" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="196" t="s">
+      <c r="C11" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="224" t="s">
         <v>2685</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="196" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="224" t="s">
         <v>2681</v>
       </c>
-      <c r="B6" s="196" t="s">
+      <c r="B12" s="224" t="s">
         <v>2682</v>
       </c>
-      <c r="C6" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="196" t="s">
+      <c r="C12" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="224" t="s">
         <v>2686</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="45">
-      <c r="A7" s="196" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="224" t="s">
         <v>2706</v>
       </c>
-      <c r="B7" s="180" t="s">
+      <c r="B13" s="222" t="s">
         <v>2707</v>
       </c>
-      <c r="C7" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="196" t="s">
+      <c r="C13" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="224" t="s">
         <v>2708</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="196" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="224" t="s">
         <v>2683</v>
       </c>
-      <c r="B8" s="196" t="s">
+      <c r="B14" s="224" t="s">
         <v>2684</v>
       </c>
-      <c r="C8" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="196" t="s">
+      <c r="C14" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="224" t="s">
         <v>2687</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="223" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="226" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="196" t="s">
+      <c r="B15" s="224" t="s">
         <v>832</v>
       </c>
-      <c r="C9" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="196" t="s">
+      <c r="C15" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="224" t="s">
         <v>2691</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="196" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" s="224" t="s">
         <v>833</v>
       </c>
-      <c r="B10" s="196" t="s">
+      <c r="B16" s="224" t="s">
         <v>834</v>
       </c>
-      <c r="C10" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="196" t="s">
+      <c r="C16" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="224" t="s">
         <v>2692</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="196" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" s="224" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B17" s="224" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C17" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="224" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="224" t="s">
         <v>1872</v>
       </c>
-      <c r="B11" s="196" t="s">
+      <c r="B18" s="224" t="s">
         <v>2690</v>
       </c>
-      <c r="C11" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="196" t="s">
+      <c r="C18" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="224" t="s">
         <v>2694</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="223" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="224" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="224" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C19" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="224" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="226" t="s">
         <v>2622</v>
       </c>
-      <c r="B12" s="196" t="s">
+      <c r="B20" s="224" t="s">
         <v>2625</v>
       </c>
-      <c r="C12" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="196" t="s">
+      <c r="C20" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="224" t="s">
         <v>2634</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="196" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="224" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B21" s="224" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C21" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="224" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="226" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B22" s="224" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C22" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="224" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="224" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B23" s="224" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C23" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="224" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="224" t="s">
         <v>1091</v>
       </c>
-      <c r="B13" s="196" t="s">
+      <c r="B24" s="224" t="s">
         <v>2629</v>
       </c>
-      <c r="C13" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="196" t="s">
+      <c r="C24" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="224" t="s">
         <v>2635</v>
       </c>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="196" t="s">
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="226" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B25" s="224" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C25" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="224" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="224" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B26" s="224" t="s">
+        <v>2633</v>
+      </c>
+      <c r="C26" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="224" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="224" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B27" s="224" t="s">
+        <v>831</v>
+      </c>
+      <c r="C27" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="224" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="224" t="s">
         <v>2636</v>
       </c>
-      <c r="B14" s="196" t="s">
+      <c r="B28" s="224" t="s">
         <v>2637</v>
       </c>
-      <c r="C14" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="196" t="s">
+      <c r="C28" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="224" t="s">
         <v>2640</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="196" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="226" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B29" s="224" t="s">
+        <v>2639</v>
+      </c>
+      <c r="C29" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="224" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="224" t="s">
         <v>1090</v>
       </c>
-      <c r="B15" s="196" t="s">
+      <c r="B30" s="224" t="s">
         <v>1316</v>
       </c>
-      <c r="C15" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="196" t="s">
+      <c r="C30" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="224" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="223" t="s">
-        <v>2720</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>2721</v>
-      </c>
-      <c r="C16" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="196" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="224" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B31" s="224" t="s">
+        <v>2641</v>
+      </c>
+      <c r="C31" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="224" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="224" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B32" s="224" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C32" s="224" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="224" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="224" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B33" s="224" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C33" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="224" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="224" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B34" s="224" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C34" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="224" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="226" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B35" s="224" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C35" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="224" t="s">
         <v>2655</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="223" t="s">
-        <v>2177</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>2722</v>
-      </c>
-      <c r="C17" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="196" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="226" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B36" s="224" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C36" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="224" t="s">
         <v>2655</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="223" t="s">
+    <row r="37" spans="1:4">
+      <c r="A37" s="226" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B37" s="224" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C37" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="224" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="226" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B38" s="224" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C38" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="224" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="224" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B39" s="224" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C39" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="224" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="224" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B40" s="222" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C40" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="224" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="226" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B41" s="224" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C41" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="224" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="226" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B42" s="224" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C42" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="224" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="224" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B43" s="222" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C43" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="224" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="226" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B44" s="222" t="s">
+        <v>884</v>
+      </c>
+      <c r="C44" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="224" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="224" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B45" s="222" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C45" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="224" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="226" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B46" s="224" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C46" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="224" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="224" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B47" s="224" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C47" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="224" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="224" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B48" s="222" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C48" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="224" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="224" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B49" s="222" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C49" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="224" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="224" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B50" s="224" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C50" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="224" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="224" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B51" s="224" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C51" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="224" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="226" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B52" s="224" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C52" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="224" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="224" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B53" s="224" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C53" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="224" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="222" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B54" s="222" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C54" s="229" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="227" t="s">
         <v>2723</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>2724</v>
-      </c>
-      <c r="C18" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="196" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="196" t="s">
-        <v>2656</v>
-      </c>
-      <c r="B19" s="196" t="s">
-        <v>2657</v>
-      </c>
-      <c r="C19" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="196" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="45">
-      <c r="A20" s="196" t="s">
-        <v>2710</v>
-      </c>
-      <c r="B20" s="180" t="s">
-        <v>2711</v>
-      </c>
-      <c r="C20" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="196" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="45">
-      <c r="A21" s="196" t="s">
-        <v>2712</v>
-      </c>
-      <c r="B21" s="180" t="s">
-        <v>2713</v>
-      </c>
-      <c r="C21" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="196" t="s">
-        <v>2662</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="45">
-      <c r="A22" s="223" t="s">
-        <v>2714</v>
-      </c>
-      <c r="B22" s="180" t="s">
-        <v>884</v>
-      </c>
-      <c r="C22" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="196" t="s">
-        <v>2662</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="223" t="s">
-        <v>2663</v>
-      </c>
-      <c r="B23" s="196" t="s">
-        <v>2664</v>
-      </c>
-      <c r="C23" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="196" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="32" t="s">
-        <v>2725</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C24" s="196"/>
-      <c r="D24" s="196"/>
-    </row>
-    <row r="25" spans="1:4" ht="45">
-      <c r="A25" s="196" t="s">
-        <v>2718</v>
-      </c>
-      <c r="B25" s="180" t="s">
-        <v>2727</v>
-      </c>
-      <c r="C25" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="196" t="s">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="196" t="s">
-        <v>2697</v>
-      </c>
-      <c r="B26" s="196" t="s">
-        <v>2698</v>
-      </c>
-      <c r="C26" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="196" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="196"/>
-      <c r="B27" s="196"/>
-      <c r="C27" s="196"/>
-      <c r="D27" s="196"/>
+      <c r="I54" s="227"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="224" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B55" s="222" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C55" s="230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="227" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I55" s="227"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="224" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B56" s="222" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C56" s="230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="227" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I56" s="227"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="224" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B57" s="222" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C57" s="230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="227" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I57" s="227"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="95" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A23" r:id="rId1" display="http://xgin.de/" xr:uid="{6D042F4B-B1B6-714D-834A-FF03BB9AF65F}"/>
-    <hyperlink ref="A12" r:id="rId2" display="http://iusq.de/" xr:uid="{B40808EF-D56C-CF4A-8448-3B54D7C1E5D4}"/>
-    <hyperlink ref="A9" r:id="rId3" display="http://zprv.de/" xr:uid="{AE8F80AC-32A6-C643-BEE6-694ECBB145F6}"/>
-    <hyperlink ref="A5" r:id="rId4" display="http://iusg.de/" xr:uid="{C28C7857-119A-4744-B0BB-4DDEA3E95E35}"/>
-    <hyperlink ref="B16" r:id="rId5" display="https://finance.yahoo.com/quote/CSBGE3.MI/" xr:uid="{07F4F9CA-E0FA-1C49-87F4-4EBCF7177C7D}"/>
-    <hyperlink ref="B17" r:id="rId6" display="https://finance.yahoo.com/quote/CSBGE7.MI/" xr:uid="{02FC7EA0-25C6-E34E-AB6A-3622B551A50D}"/>
-    <hyperlink ref="B18" r:id="rId7" display="https://finance.yahoo.com/quote/SXRQ.DE/" xr:uid="{4E4D2C26-5E71-C644-AF09-EF7691622628}"/>
-    <hyperlink ref="A24" r:id="rId8" display="https://finance.yahoo.com/quote/XEIN.DE/" xr:uid="{6DA783E3-A09C-7C47-88D8-23C14B21E7FE}"/>
-    <hyperlink ref="B24" r:id="rId9" display="https://finance.yahoo.com/quote/XEIN.DE/" xr:uid="{894A731F-3358-3D4B-A900-50AD652ED5AE}"/>
+    <hyperlink ref="A25" r:id="rId1" display="http://eunl.de/" xr:uid="{D3B831DB-7BE7-EC44-955D-8D4AD5648109}"/>
+    <hyperlink ref="A29" r:id="rId2" display="http://exie.de/" xr:uid="{7DBF71AB-E5A1-5746-9594-6331DE72FAE7}"/>
+    <hyperlink ref="A35" r:id="rId3" display="http://exx5.de/" xr:uid="{5C3F1F21-80A6-6A4B-A3F1-C170887BAA29}"/>
+    <hyperlink ref="A36" r:id="rId4" display="http://ibgs.de/" xr:uid="{92F746C5-6C2D-5E4C-8107-ABE070ABCF1B}"/>
+    <hyperlink ref="A37" r:id="rId5" display="http://ibgm.de/" xr:uid="{137FD5CA-DBBD-4149-94B0-313F2BDF75A4}"/>
+    <hyperlink ref="A38" r:id="rId6" display="http://ibgl.de/" xr:uid="{E778104F-911E-9041-93A8-3A9890FB40FA}"/>
+    <hyperlink ref="A41" r:id="rId7" display="http://syb3.de/" xr:uid="{3F07D3A7-CB3E-DF42-A772-B81D54307B79}"/>
+    <hyperlink ref="A42" r:id="rId8" display="http://sybj.de/" xr:uid="{7F610E34-ACD3-DD4A-8819-4877AC0613CC}"/>
+    <hyperlink ref="A46" r:id="rId9" display="http://xgin.de/" xr:uid="{FE6C00CE-0666-D046-A54D-3A05574F5932}"/>
+    <hyperlink ref="A5" r:id="rId10" display="http://anx.pa/" xr:uid="{4E2FF11F-CC90-9543-AEB1-8ED135CA0767}"/>
+    <hyperlink ref="A22" r:id="rId11" display="http://spyy.de/" xr:uid="{2E86905F-4F36-DC4C-9E0F-FF951E5DDE34}"/>
+    <hyperlink ref="A8" r:id="rId12" display="http://sxr8.de/" xr:uid="{0B9D1115-496D-104F-BC65-37D3CB47E4AA}"/>
+    <hyperlink ref="A20" r:id="rId13" display="http://iusq.de/" xr:uid="{94F776A8-EC0C-4944-83DD-EF5A8171B4BA}"/>
+    <hyperlink ref="A15" r:id="rId14" display="http://zprv.de/" xr:uid="{0524365E-F75D-7048-A342-2C26A764439D}"/>
+    <hyperlink ref="A52" r:id="rId15" display="http://xad5.de/" xr:uid="{91683560-1C3A-9B4A-874F-B7AB28F86B38}"/>
+    <hyperlink ref="A11" r:id="rId16" display="http://iusg.de/" xr:uid="{57403CF9-697A-4A4E-8DBB-67A85627F664}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
@@ -60682,785 +59700,2066 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C41D104-D122-ED4F-9557-76507CFD2D71}">
-  <dimension ref="A1:D54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A71EAAD3-1C46-AE43-AEF2-56898A879CDD}">
+  <dimension ref="A1:J178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="78.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="224" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B1" s="225" t="s">
-        <v>2121</v>
-      </c>
-      <c r="C1" s="221" t="s">
-        <v>2122</v>
-      </c>
-      <c r="D1" s="221" t="s">
-        <v>2703</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    <row r="1" spans="1:10" ht="23">
+      <c r="A1" s="18" t="s">
+        <v>710</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="D1" s="15"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="12"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="197" t="s">
-        <v>820</v>
-      </c>
-      <c r="B2" s="222" t="s">
-        <v>1032</v>
+        <v>2</v>
+      </c>
+      <c r="B2" s="198" t="s">
+        <v>2549</v>
       </c>
       <c r="C2" s="199" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="196" t="s">
-        <v>2695</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="194" t="s">
-        <v>2619</v>
-      </c>
-      <c r="B3" s="222" t="s">
-        <v>2620</v>
-      </c>
-      <c r="C3" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="196" t="s">
-        <v>2696</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="196" t="s">
-        <v>2668</v>
-      </c>
-      <c r="B4" s="196" t="s">
-        <v>2669</v>
-      </c>
-      <c r="C4" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="196" t="s">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="223" t="s">
-        <v>2670</v>
-      </c>
-      <c r="B5" s="196" t="s">
-        <v>2671</v>
-      </c>
-      <c r="C5" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="196" t="s">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="196" t="s">
-        <v>2132</v>
-      </c>
-      <c r="B6" s="196" t="s">
-        <v>2672</v>
-      </c>
-      <c r="C6" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="196" t="s">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="196" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B7" s="196" t="s">
-        <v>2674</v>
-      </c>
-      <c r="C7" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="196" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="223" t="s">
-        <v>2675</v>
-      </c>
-      <c r="B8" s="196" t="s">
-        <v>2676</v>
-      </c>
-      <c r="C8" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="196" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="196" t="s">
-        <v>2677</v>
-      </c>
-      <c r="B9" s="196" t="s">
-        <v>2678</v>
-      </c>
-      <c r="C9" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="196" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="196" t="s">
-        <v>2679</v>
-      </c>
-      <c r="B10" s="196" t="s">
-        <v>2678</v>
-      </c>
-      <c r="C10" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="196" t="s">
-        <v>2680</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="45">
-      <c r="A11" s="223" t="s">
-        <v>2704</v>
-      </c>
-      <c r="B11" s="180" t="s">
-        <v>2705</v>
-      </c>
-      <c r="C11" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="196" t="s">
-        <v>2685</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="196" t="s">
-        <v>2681</v>
-      </c>
-      <c r="B12" s="196" t="s">
-        <v>2682</v>
-      </c>
-      <c r="C12" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="196" t="s">
-        <v>2686</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="45">
-      <c r="A13" s="196" t="s">
-        <v>2706</v>
-      </c>
-      <c r="B13" s="180" t="s">
-        <v>2707</v>
-      </c>
-      <c r="C13" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="196" t="s">
-        <v>2708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="196" t="s">
-        <v>2683</v>
-      </c>
-      <c r="B14" s="196" t="s">
-        <v>2684</v>
-      </c>
-      <c r="C14" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="196" t="s">
-        <v>2687</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="223" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="197" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B3" s="198" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C3" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" ht="45">
+      <c r="A4" s="180" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B4" s="198" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C4" s="199" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="197" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B5" s="198" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C5" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="197" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="196" t="s">
-        <v>832</v>
-      </c>
-      <c r="C15" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="196" t="s">
-        <v>2691</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="196" t="s">
-        <v>833</v>
-      </c>
-      <c r="B16" s="196" t="s">
-        <v>834</v>
-      </c>
-      <c r="C16" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="196" t="s">
-        <v>2692</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="196" t="s">
-        <v>2688</v>
-      </c>
-      <c r="B17" s="196" t="s">
-        <v>2689</v>
-      </c>
-      <c r="C17" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="196" t="s">
-        <v>2693</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="196" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B18" s="196" t="s">
-        <v>2690</v>
-      </c>
-      <c r="C18" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="196" t="s">
-        <v>2694</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="196" t="s">
+      <c r="B6" s="198" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C6" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="197" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="196" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C19" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="196" t="s">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="223" t="s">
-        <v>2622</v>
-      </c>
-      <c r="B20" s="196" t="s">
-        <v>2625</v>
-      </c>
-      <c r="C20" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="196" t="s">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="196" t="s">
-        <v>2623</v>
-      </c>
-      <c r="B21" s="196" t="s">
-        <v>2626</v>
-      </c>
-      <c r="C21" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="196" t="s">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="223" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B22" s="196" t="s">
-        <v>2627</v>
-      </c>
-      <c r="C22" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="196" t="s">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="196" t="s">
-        <v>2624</v>
-      </c>
-      <c r="B23" s="196" t="s">
-        <v>2628</v>
-      </c>
-      <c r="C23" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="196" t="s">
-        <v>2634</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="196" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B24" s="196" t="s">
-        <v>2629</v>
-      </c>
-      <c r="C24" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="196" t="s">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="223" t="s">
-        <v>2630</v>
-      </c>
-      <c r="B25" s="196" t="s">
-        <v>2631</v>
-      </c>
-      <c r="C25" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="196" t="s">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="196" t="s">
-        <v>2632</v>
-      </c>
-      <c r="B26" s="196" t="s">
-        <v>2633</v>
-      </c>
-      <c r="C26" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="196" t="s">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="196" t="s">
-        <v>1753</v>
-      </c>
-      <c r="B27" s="196" t="s">
-        <v>831</v>
-      </c>
-      <c r="C27" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="196" t="s">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="196" t="s">
-        <v>2636</v>
-      </c>
-      <c r="B28" s="196" t="s">
-        <v>2637</v>
-      </c>
-      <c r="C28" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="196" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="223" t="s">
-        <v>2638</v>
-      </c>
-      <c r="B29" s="196" t="s">
-        <v>2639</v>
-      </c>
-      <c r="C29" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="196" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="196" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B30" s="196" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C30" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="196" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="196" t="s">
-        <v>2324</v>
-      </c>
-      <c r="B31" s="196" t="s">
-        <v>2641</v>
-      </c>
-      <c r="C31" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="196" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="196" t="s">
-        <v>2642</v>
-      </c>
-      <c r="B32" s="196" t="s">
-        <v>2643</v>
-      </c>
-      <c r="C32" s="196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="196" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="196" t="s">
-        <v>2645</v>
-      </c>
-      <c r="B33" s="196" t="s">
-        <v>2646</v>
-      </c>
-      <c r="C33" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="196" t="s">
-        <v>2651</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="196" t="s">
-        <v>2647</v>
-      </c>
-      <c r="B34" s="196" t="s">
-        <v>2648</v>
-      </c>
-      <c r="C34" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="196" t="s">
-        <v>2651</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="223" t="s">
-        <v>2649</v>
-      </c>
-      <c r="B35" s="196" t="s">
-        <v>2650</v>
-      </c>
-      <c r="C35" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="196" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="223" t="s">
-        <v>2709</v>
-      </c>
-      <c r="B36" s="196" t="s">
-        <v>2652</v>
-      </c>
-      <c r="C36" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="196" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="223" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B37" s="196" t="s">
-        <v>2653</v>
-      </c>
-      <c r="C37" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="196" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="223" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B38" s="196" t="s">
-        <v>2654</v>
-      </c>
-      <c r="C38" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="196" t="s">
-        <v>2655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="196" t="s">
-        <v>2656</v>
-      </c>
-      <c r="B39" s="196" t="s">
-        <v>2657</v>
-      </c>
-      <c r="C39" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="196" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="45">
-      <c r="A40" s="196" t="s">
-        <v>2710</v>
-      </c>
-      <c r="B40" s="180" t="s">
-        <v>2711</v>
-      </c>
-      <c r="C40" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="196" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="223" t="s">
-        <v>2658</v>
-      </c>
-      <c r="B41" s="196" t="s">
-        <v>2659</v>
-      </c>
-      <c r="C41" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="196" t="s">
-        <v>2660</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="223" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B42" s="196" t="s">
-        <v>2661</v>
-      </c>
-      <c r="C42" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="196" t="s">
-        <v>2662</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="45">
-      <c r="A43" s="196" t="s">
-        <v>2712</v>
-      </c>
-      <c r="B43" s="180" t="s">
-        <v>2713</v>
-      </c>
-      <c r="C43" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="196" t="s">
-        <v>2662</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="45">
-      <c r="A44" s="223" t="s">
-        <v>2714</v>
-      </c>
-      <c r="B44" s="180" t="s">
-        <v>884</v>
-      </c>
-      <c r="C44" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="196" t="s">
-        <v>2662</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="45">
-      <c r="A45" s="196" t="s">
-        <v>2090</v>
-      </c>
-      <c r="B45" s="180" t="s">
-        <v>2715</v>
-      </c>
-      <c r="C45" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="196" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="223" t="s">
-        <v>2663</v>
-      </c>
-      <c r="B46" s="196" t="s">
-        <v>2664</v>
-      </c>
-      <c r="C46" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="196" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="196" t="s">
-        <v>2411</v>
-      </c>
-      <c r="B47" s="196" t="s">
-        <v>2665</v>
-      </c>
-      <c r="C47" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="196" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="45">
-      <c r="A48" s="196" t="s">
-        <v>2716</v>
-      </c>
-      <c r="B48" s="180" t="s">
-        <v>2717</v>
-      </c>
-      <c r="C48" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="196" t="s">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="45">
-      <c r="A49" s="196" t="s">
-        <v>2718</v>
-      </c>
-      <c r="B49" s="180" t="s">
-        <v>2719</v>
-      </c>
-      <c r="C49" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="196" t="s">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="196" t="s">
-        <v>2697</v>
-      </c>
-      <c r="B50" s="196" t="s">
-        <v>2698</v>
-      </c>
-      <c r="C50" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="196" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="196" t="s">
-        <v>2135</v>
-      </c>
-      <c r="B51" s="196" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C51" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D51" s="196" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="223" t="s">
-        <v>2699</v>
-      </c>
-      <c r="B52" s="196" t="s">
-        <v>2700</v>
-      </c>
-      <c r="C52" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="196" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="196" t="s">
-        <v>2701</v>
-      </c>
-      <c r="B53" s="196" t="s">
-        <v>2702</v>
-      </c>
-      <c r="C53" s="196" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="196" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="196"/>
-      <c r="B54" s="196"/>
-      <c r="C54" s="196"/>
-      <c r="D54" s="196"/>
+      <c r="B7" s="198" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C7" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="197" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B8" s="198" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C8" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="197" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B9" s="198" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C9" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="197" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B10" s="198" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C10" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="197" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B11" s="198" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C11" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" ht="23">
+      <c r="A12" s="197" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B12" s="198" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C12" s="199" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="197" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B13" s="198" t="s">
+        <v>2559</v>
+      </c>
+      <c r="C13" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="197" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B14" s="198" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C14" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="197" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B15" s="198" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C15" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="197" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B16" s="198" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C16" s="199" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="197" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B17" s="198" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C17" s="199" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="197" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B18" s="198" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C18" s="199" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="197" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B19" s="198" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C19" s="199" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="1:9" ht="45">
+      <c r="A20" s="180" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B20" s="180" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C20" s="219" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="1:9" ht="45">
+      <c r="A21" s="19" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B21" s="180" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C21" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" spans="1:9" ht="45">
+      <c r="A22" s="19" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B22" s="180" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C22" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" spans="1:9" ht="45">
+      <c r="A23" s="19" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B23" s="180" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C23" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" spans="1:9" ht="45">
+      <c r="A24" s="180" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B24" s="180" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C24" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" spans="1:9" ht="45">
+      <c r="A25" s="180" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B25" s="180" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C25" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" spans="1:9" ht="45">
+      <c r="A26" s="180" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B26" s="180" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C26" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" spans="1:9" ht="45">
+      <c r="A27" s="180" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B27" s="180" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C27" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" spans="1:9" ht="45">
+      <c r="A28" s="180" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B28" s="180" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C28" s="220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" spans="1:9" ht="45">
+      <c r="A29" s="180" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B29" s="180" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C29" s="220" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" spans="1:9" ht="45">
+      <c r="A30" s="180" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B30" s="180" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C30" s="220" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" spans="1:9" ht="18">
+      <c r="A31" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="18">
+      <c r="A32" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18">
+      <c r="A33" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18">
+      <c r="A34" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18">
+      <c r="A35" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18">
+      <c r="A36" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18">
+      <c r="A37" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18">
+      <c r="A38" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18">
+      <c r="A39" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18">
+      <c r="A40" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18">
+      <c r="A41" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18">
+      <c r="A42" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18">
+      <c r="A43" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18">
+      <c r="A44" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="18">
+      <c r="A45" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18">
+      <c r="A46" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18">
+      <c r="A47" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18">
+      <c r="A48" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18">
+      <c r="A49" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18">
+      <c r="A50" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18">
+      <c r="A51" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18">
+      <c r="A52" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18">
+      <c r="A53" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18">
+      <c r="A54" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18">
+      <c r="A55" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18">
+      <c r="A56" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18">
+      <c r="A57" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18">
+      <c r="A58" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18">
+      <c r="A59" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18">
+      <c r="A60" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="18">
+      <c r="A61" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="18">
+      <c r="A62" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="18">
+      <c r="A63" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="18">
+      <c r="A64" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="18">
+      <c r="A65" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="18">
+      <c r="A66" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C66" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="18">
+      <c r="A67" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="18">
+      <c r="A68" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="18">
+      <c r="A69" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="C69" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="18">
+      <c r="A70" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C70" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="18">
+      <c r="A71" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="18">
+      <c r="A72" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C72" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="18">
+      <c r="A73" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="18">
+      <c r="A74" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C74" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="18">
+      <c r="A75" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="18">
+      <c r="A76" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C76" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="18">
+      <c r="A77" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C77" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="18">
+      <c r="A78" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C78" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="18">
+      <c r="A79" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="18">
+      <c r="A80" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C80" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="18">
+      <c r="A81" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="C81" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="18">
+      <c r="A82" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="18">
+      <c r="A83" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C83" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="18">
+      <c r="A84" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C84" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="18">
+      <c r="A85" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C85" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="18">
+      <c r="A86" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C86" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="18">
+      <c r="A87" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C87" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="18">
+      <c r="A88" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C88" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="18">
+      <c r="A89" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C89" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="18">
+      <c r="A90" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C90" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="18">
+      <c r="A91" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C91" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="18">
+      <c r="A92" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="C92" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="18">
+      <c r="A93" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="C93" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="18">
+      <c r="A94" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="C94" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="18">
+      <c r="A95" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="18">
+      <c r="A96" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="C96" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="18">
+      <c r="A97" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="C97" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="18">
+      <c r="A98" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C98" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="18">
+      <c r="A99" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="C99" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="18">
+      <c r="A100" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="C100" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="18">
+      <c r="A101" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C101" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="18">
+      <c r="A102" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C102" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="18">
+      <c r="A103" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C103" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="18">
+      <c r="A104" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="B104" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="C104" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="18">
+      <c r="A105" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="C105" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="18">
+      <c r="A106" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C106" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="18">
+      <c r="A107" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C107" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="18">
+      <c r="A108" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="C108" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="18">
+      <c r="A109" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C109" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="18">
+      <c r="A110" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="B110" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="C110" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="18">
+      <c r="A111" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="C111" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="18">
+      <c r="A112" s="27" t="s">
+        <v>412</v>
+      </c>
+      <c r="B112" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C112" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="18">
+      <c r="A113" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="C113" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="18">
+      <c r="A114" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="B114" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="C114" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="18">
+      <c r="A115" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="C115" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="18">
+      <c r="A116" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C116" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="18">
+      <c r="A117" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C117" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="18">
+      <c r="A118" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>437</v>
+      </c>
+      <c r="C118" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="18">
+      <c r="A119" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="C119" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="18">
+      <c r="A120" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="C120" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="18">
+      <c r="A121" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="C121" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="18">
+      <c r="A122" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="C122" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="18">
+      <c r="A123" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="C123" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="18">
+      <c r="A124" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>461</v>
+      </c>
+      <c r="C124" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="18">
+      <c r="A125" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>465</v>
+      </c>
+      <c r="C125" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="18">
+      <c r="A126" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="C126" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="18">
+      <c r="A127" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="C127" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="18">
+      <c r="A128" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="C128" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="18">
+      <c r="A129" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="C129" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="18">
+      <c r="A130" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="C130" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="18">
+      <c r="A131" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="C131" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="18">
+      <c r="A132" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="B132" s="27" t="s">
+        <v>493</v>
+      </c>
+      <c r="C132" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="18">
+      <c r="A133" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="B133" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="C133" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="18">
+      <c r="A134" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="B134" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="C134" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="18">
+      <c r="A135" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="C135" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="18">
+      <c r="A136" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="B136" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="C136" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="18">
+      <c r="A137" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B137" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="C137" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="18">
+      <c r="A138" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="C138" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="18">
+      <c r="A139" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="C139" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="18">
+      <c r="A140" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="B140" s="27" t="s">
+        <v>525</v>
+      </c>
+      <c r="C140" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="18">
+      <c r="A141" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="C141" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="18">
+      <c r="A142" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="B142" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="C142" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="18">
+      <c r="A143" s="27" t="s">
+        <v>536</v>
+      </c>
+      <c r="B143" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="C143" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="18">
+      <c r="A144" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="B144" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="C144" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="18">
+      <c r="A145" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="B145" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="C145" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="18">
+      <c r="A146" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="C146" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="18">
+      <c r="A147" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="C147" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="18">
+      <c r="A148" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="27" t="s">
+        <v>556</v>
+      </c>
+      <c r="C148" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="18">
+      <c r="A149" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="B149" s="27" t="s">
+        <v>562</v>
+      </c>
+      <c r="C149" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="18">
+      <c r="A150" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="B150" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="C150" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="18">
+      <c r="A151" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="B151" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="C151" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="18">
+      <c r="A152" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="B152" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="C152" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="18">
+      <c r="A153" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="C153" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="18">
+      <c r="A154" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="B154" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="C154" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="18">
+      <c r="A155" s="27" t="s">
+        <v>585</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>586</v>
+      </c>
+      <c r="C155" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="18">
+      <c r="A156" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="B156" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="C156" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="18">
+      <c r="A157" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>594</v>
+      </c>
+      <c r="C157" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="18">
+      <c r="A158" s="27" t="s">
+        <v>597</v>
+      </c>
+      <c r="B158" s="27" t="s">
+        <v>598</v>
+      </c>
+      <c r="C158" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="18">
+      <c r="A159" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="C159" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="18">
+      <c r="A160" s="27" t="s">
+        <v>605</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>606</v>
+      </c>
+      <c r="C160" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="18">
+      <c r="A161" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="B161" s="27" t="s">
+        <v>610</v>
+      </c>
+      <c r="C161" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="18">
+      <c r="A162" s="27" t="s">
+        <v>613</v>
+      </c>
+      <c r="B162" s="27" t="s">
+        <v>614</v>
+      </c>
+      <c r="C162" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="18">
+      <c r="A163" s="27" t="s">
+        <v>617</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>618</v>
+      </c>
+      <c r="C163" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="18">
+      <c r="A164" s="27" t="s">
+        <v>621</v>
+      </c>
+      <c r="B164" s="27" t="s">
+        <v>622</v>
+      </c>
+      <c r="C164" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="18">
+      <c r="A165" s="27" t="s">
+        <v>625</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>626</v>
+      </c>
+      <c r="C165" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="18">
+      <c r="A166" s="27" t="s">
+        <v>629</v>
+      </c>
+      <c r="B166" s="27" t="s">
+        <v>630</v>
+      </c>
+      <c r="C166" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="18">
+      <c r="A167" s="27" t="s">
+        <v>633</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="C167" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="18">
+      <c r="A168" s="27" t="s">
+        <v>637</v>
+      </c>
+      <c r="B168" s="27" t="s">
+        <v>638</v>
+      </c>
+      <c r="C168" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="18">
+      <c r="A169" s="27" t="s">
+        <v>641</v>
+      </c>
+      <c r="B169" s="27" t="s">
+        <v>642</v>
+      </c>
+      <c r="C169" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="18">
+      <c r="A170" s="27" t="s">
+        <v>645</v>
+      </c>
+      <c r="B170" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="C170" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="18">
+      <c r="A171" s="27" t="s">
+        <v>649</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>650</v>
+      </c>
+      <c r="C171" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="18">
+      <c r="A172" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="B172" s="27" t="s">
+        <v>654</v>
+      </c>
+      <c r="C172" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="18">
+      <c r="A173" s="27" t="s">
+        <v>657</v>
+      </c>
+      <c r="B173" s="27" t="s">
+        <v>658</v>
+      </c>
+      <c r="C173" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="18">
+      <c r="A174" s="27" t="s">
+        <v>661</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>662</v>
+      </c>
+      <c r="C174" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="18">
+      <c r="A175" s="27" t="s">
+        <v>665</v>
+      </c>
+      <c r="B175" s="27" t="s">
+        <v>666</v>
+      </c>
+      <c r="C175" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="18">
+      <c r="A176" s="27" t="s">
+        <v>669</v>
+      </c>
+      <c r="B176" s="27" t="s">
+        <v>670</v>
+      </c>
+      <c r="C176" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="18">
+      <c r="A177" s="27" t="s">
+        <v>673</v>
+      </c>
+      <c r="B177" s="27" t="s">
+        <v>674</v>
+      </c>
+      <c r="C177" s="172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="18">
+      <c r="A178" s="27" t="s">
+        <v>677</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="C178" s="172" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A25" r:id="rId1" display="http://eunl.de/" xr:uid="{D3B831DB-7BE7-EC44-955D-8D4AD5648109}"/>
-    <hyperlink ref="A29" r:id="rId2" display="http://exie.de/" xr:uid="{7DBF71AB-E5A1-5746-9594-6331DE72FAE7}"/>
-    <hyperlink ref="A35" r:id="rId3" display="http://exx5.de/" xr:uid="{5C3F1F21-80A6-6A4B-A3F1-C170887BAA29}"/>
-    <hyperlink ref="A36" r:id="rId4" display="http://ibgs.de/" xr:uid="{92F746C5-6C2D-5E4C-8107-ABE070ABCF1B}"/>
-    <hyperlink ref="A37" r:id="rId5" display="http://ibgm.de/" xr:uid="{137FD5CA-DBBD-4149-94B0-313F2BDF75A4}"/>
-    <hyperlink ref="A38" r:id="rId6" display="http://ibgl.de/" xr:uid="{E778104F-911E-9041-93A8-3A9890FB40FA}"/>
-    <hyperlink ref="A41" r:id="rId7" display="http://syb3.de/" xr:uid="{3F07D3A7-CB3E-DF42-A772-B81D54307B79}"/>
-    <hyperlink ref="A42" r:id="rId8" display="http://sybj.de/" xr:uid="{7F610E34-ACD3-DD4A-8819-4877AC0613CC}"/>
-    <hyperlink ref="A46" r:id="rId9" display="http://xgin.de/" xr:uid="{FE6C00CE-0666-D046-A54D-3A05574F5932}"/>
-    <hyperlink ref="A5" r:id="rId10" display="http://anx.pa/" xr:uid="{4E2FF11F-CC90-9543-AEB1-8ED135CA0767}"/>
-    <hyperlink ref="A22" r:id="rId11" display="http://spyy.de/" xr:uid="{2E86905F-4F36-DC4C-9E0F-FF951E5DDE34}"/>
-    <hyperlink ref="A8" r:id="rId12" display="http://sxr8.de/" xr:uid="{0B9D1115-496D-104F-BC65-37D3CB47E4AA}"/>
-    <hyperlink ref="A20" r:id="rId13" display="http://iusq.de/" xr:uid="{94F776A8-EC0C-4944-83DD-EF5A8171B4BA}"/>
-    <hyperlink ref="A15" r:id="rId14" display="http://zprv.de/" xr:uid="{0524365E-F75D-7048-A342-2C26A764439D}"/>
-    <hyperlink ref="A52" r:id="rId15" display="http://xad5.de/" xr:uid="{91683560-1C3A-9B4A-874F-B7AB28F86B38}"/>
-    <hyperlink ref="A11" r:id="rId16" display="http://iusg.de/" xr:uid="{57403CF9-697A-4A4E-8DBB-67A85627F664}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId17"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/Files/ETF.xlsx
+++ b/Files/ETF.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SIMBOLO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DESCRIZIONE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>VALUTA</t>
         </is>

--- a/Files/ETF.xlsx
+++ b/Files/ETF.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
